--- a/data/winter_spring_data.xlsx
+++ b/data/winter_spring_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="冬季" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="60">
   <si>
     <t>采样点</t>
   </si>
@@ -168,9 +168,6 @@
     <t>气温/℃</t>
   </si>
   <si>
-    <t>泥水状况</t>
-  </si>
-  <si>
     <t>DO(mg/L)</t>
   </si>
   <si>
@@ -249,51 +246,10 @@
     <t>R1</t>
   </si>
   <si>
-    <t>无水无泥</t>
-  </si>
-  <si>
     <t>R2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水泥少</t>
-    </r>
-  </si>
-  <si>
     <t>R3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水无泥</t>
-    </r>
   </si>
   <si>
     <t>R4</t>
@@ -414,47 +370,6 @@
   <si>
     <t>（固）硝态氮（mg/kg）</t>
   </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFC00000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>有水</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无泥</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无水</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="30"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>有泥</t>
-    </r>
-  </si>
-  <si>
-    <t>R14(溢出)</t>
-  </si>
 </sst>
 </file>
 
@@ -468,7 +383,7 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,7 +415,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="8" tint="-0.25"/>
+      <color theme="8" tint="-0.249977111117893"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -508,7 +423,7 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="8" tint="-0.25"/>
+      <color theme="8" tint="-0.249977111117893"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -524,22 +439,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFC00000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="7" tint="-0.25"/>
+      <color theme="7" tint="-0.249977111117893"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -553,12 +455,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -567,7 +463,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="4" tint="-0.25"/>
+      <color theme="4" tint="-0.249977111117893"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -718,20 +614,14 @@
     </font>
     <font>
       <b/>
-      <vertAlign val="subscript"/>
-      <sz val="12"/>
+      <sz val="8"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <vertAlign val="subscript"/>
       <sz val="12"/>
-      <color indexed="30"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -745,7 +635,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1090,152 +980,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1308,12 +1198,6 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1338,34 +1222,31 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1684,7 +1565,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA40"/>
+  <dimension ref="A1:Z40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="14.125" style="1"/>
@@ -1694,107 +1575,104 @@
     <col min="7" max="7" width="10.25" customWidth="1"/>
     <col min="8" max="8" width="12.875" customWidth="1"/>
     <col min="9" max="9" width="11.875" customWidth="1"/>
-    <col min="18" max="19" width="15" customWidth="1"/>
-    <col min="20" max="21" width="13.125" customWidth="1"/>
-    <col min="22" max="22" width="15.875" customWidth="1"/>
-    <col min="23" max="23" width="15.25" customWidth="1"/>
-    <col min="25" max="25" width="10.375"/>
+    <col min="17" max="18" width="15" customWidth="1"/>
+    <col min="19" max="20" width="13.125" customWidth="1"/>
+    <col min="21" max="21" width="15.875" customWidth="1"/>
+    <col min="22" max="22" width="15.25" customWidth="1"/>
+    <col min="24" max="24" width="10.375"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:27">
-      <c r="A1" s="26" t="s">
+    <row r="1" ht="16.5" spans="1:26">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="28" t="s">
+      <c r="L1" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="M1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="28" t="s">
+      <c r="O1" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="28" t="s">
+      <c r="P1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="R1" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="S1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="31" t="s">
+      <c r="U1" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="32" t="s">
+      <c r="V1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="W1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="28" t="s">
+      <c r="Z1" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="33" t="s">
+    </row>
+    <row r="2" ht="14.25" spans="1:26">
+      <c r="A2" s="32" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" ht="14.25" spans="1:27">
-      <c r="A2" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="35">
+      <c r="B2" s="33">
         <v>3.53206333333333</v>
       </c>
-      <c r="C2" s="35">
+      <c r="C2" s="33">
         <v>0.417564</v>
       </c>
-      <c r="D2" s="36">
+      <c r="D2" s="34">
         <v>702</v>
       </c>
       <c r="E2" s="18">
@@ -1806,42 +1684,39 @@
       <c r="G2" s="18">
         <v>20.9</v>
       </c>
-      <c r="H2" s="36">
+      <c r="H2" s="34">
         <v>554</v>
       </c>
       <c r="I2" s="18">
         <v>326</v>
       </c>
-      <c r="J2" s="33">
+      <c r="J2" s="31">
         <v>14</v>
       </c>
-      <c r="K2" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="33"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="18"/>
       <c r="N2" s="18"/>
       <c r="O2" s="18"/>
       <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="Z2" s="18">
+      <c r="Y2" s="18">
         <v>1.16</v>
       </c>
-      <c r="AA2" s="23">
+      <c r="Z2" s="23">
         <v>0.416666666666667</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:27">
-      <c r="A3" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="35">
+    <row r="3" ht="14.25" spans="1:26">
+      <c r="A3" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="33">
         <v>2.28796333333333</v>
       </c>
-      <c r="C3" s="35">
+      <c r="C3" s="33">
         <v>0.43909</v>
       </c>
-      <c r="D3" s="36">
+      <c r="D3" s="34">
         <v>1076</v>
       </c>
       <c r="E3" s="18">
@@ -1853,76 +1728,73 @@
       <c r="G3" s="18">
         <v>20.9</v>
       </c>
-      <c r="H3" s="36">
+      <c r="H3" s="34">
         <v>784</v>
       </c>
       <c r="I3" s="18">
         <v>330</v>
       </c>
-      <c r="J3" s="33">
+      <c r="J3" s="31">
         <v>13</v>
       </c>
-      <c r="K3" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="18">
+      <c r="K3" s="18">
         <v>5.42</v>
       </c>
-      <c r="M3" s="33">
+      <c r="L3" s="31">
         <v>739</v>
       </c>
+      <c r="M3" s="18">
+        <v>1156</v>
+      </c>
       <c r="N3" s="18">
-        <v>1156</v>
+        <v>10.3</v>
       </c>
       <c r="O3" s="18">
-        <v>10.3</v>
-      </c>
-      <c r="P3" s="18">
         <v>7.16</v>
       </c>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="38">
+      <c r="P3" s="18"/>
+      <c r="Q3" s="35">
         <v>54.08</v>
       </c>
-      <c r="S3" s="39">
+      <c r="R3" s="36">
         <v>183.4</v>
       </c>
-      <c r="T3" s="39">
+      <c r="S3" s="36">
         <v>129.3</v>
       </c>
-      <c r="U3" s="38">
+      <c r="T3" s="35">
         <v>122.55</v>
       </c>
-      <c r="V3" s="38">
+      <c r="U3" s="35">
         <v>8.4</v>
       </c>
-      <c r="W3" s="38">
+      <c r="V3" s="35">
         <v>114.05</v>
       </c>
-      <c r="X3" s="38">
+      <c r="W3" s="35">
         <v>0.95</v>
       </c>
-      <c r="Y3" s="38">
+      <c r="X3" s="35">
         <v>1713.08</v>
       </c>
-      <c r="Z3" s="18">
+      <c r="Y3" s="18">
         <v>1.16</v>
       </c>
-      <c r="AA3" s="23">
+      <c r="Z3" s="23">
         <v>0.434027777777778</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:27">
-      <c r="A4" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="35">
+    <row r="4" ht="14.25" spans="1:26">
+      <c r="A4" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="33">
         <v>2.30093666666667</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="33">
         <v>0.382523333333333</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="34">
         <v>953</v>
       </c>
       <c r="E4" s="18">
@@ -1934,76 +1806,73 @@
       <c r="G4" s="18">
         <v>20.9</v>
       </c>
-      <c r="H4" s="36">
+      <c r="H4" s="34">
         <v>819</v>
       </c>
       <c r="I4" s="18">
         <v>309</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="31">
         <v>14</v>
       </c>
-      <c r="K4" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="18">
+      <c r="K4" s="18">
         <v>6.93</v>
       </c>
-      <c r="M4" s="33">
+      <c r="L4" s="31">
         <v>365</v>
       </c>
+      <c r="M4" s="18">
+        <v>625</v>
+      </c>
       <c r="N4" s="18">
-        <v>625</v>
+        <v>16.7</v>
       </c>
       <c r="O4" s="18">
-        <v>16.7</v>
-      </c>
-      <c r="P4" s="18">
         <v>7.28</v>
       </c>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="38">
+      <c r="P4" s="18"/>
+      <c r="Q4" s="35">
         <v>21.42</v>
       </c>
-      <c r="S4" s="39">
+      <c r="R4" s="36">
         <v>106.6</v>
       </c>
-      <c r="T4" s="39">
+      <c r="S4" s="36">
         <v>85.16</v>
       </c>
-      <c r="U4" s="38">
+      <c r="T4" s="35">
         <v>54.73</v>
       </c>
-      <c r="V4" s="38">
+      <c r="U4" s="35">
         <v>1.18</v>
       </c>
-      <c r="W4" s="38">
+      <c r="V4" s="35">
         <v>27.76</v>
       </c>
-      <c r="X4" s="38">
+      <c r="W4" s="35">
         <v>2.04</v>
       </c>
-      <c r="Y4" s="38">
+      <c r="X4" s="35">
         <v>574.91</v>
       </c>
-      <c r="Z4" s="18">
+      <c r="Y4" s="18">
         <v>1.15</v>
       </c>
-      <c r="AA4" s="23">
+      <c r="Z4" s="23">
         <v>0.692361111111111</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:27">
-      <c r="A5" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="35">
+    <row r="5" ht="14.25" spans="1:26">
+      <c r="A5" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="33">
         <v>2.36703</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <v>0.392849</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="34">
         <v>630</v>
       </c>
       <c r="E5" s="18">
@@ -2015,42 +1884,39 @@
       <c r="G5" s="18">
         <v>20.9</v>
       </c>
-      <c r="H5" s="40">
+      <c r="H5" s="37">
         <v>869</v>
       </c>
       <c r="I5" s="18">
         <v>326</v>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="31">
         <v>14</v>
       </c>
-      <c r="K5" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="18"/>
-      <c r="M5" s="33"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="18"/>
       <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="Z5" s="18">
+      <c r="Y5" s="18">
         <v>1.15</v>
       </c>
-      <c r="AA5" s="23">
+      <c r="Z5" s="23">
         <v>0.681944444444444</v>
       </c>
     </row>
-    <row r="6" ht="14.25" spans="1:27">
-      <c r="A6" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="35">
+    <row r="6" ht="14.25" spans="1:26">
+      <c r="A6" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="33">
         <v>2.23916333333333</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="33">
         <v>0.416533666666667</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="34">
         <v>630</v>
       </c>
       <c r="E6" s="18">
@@ -2062,42 +1928,39 @@
       <c r="G6" s="18">
         <v>20.9</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="34">
         <v>718</v>
       </c>
       <c r="I6" s="18">
         <v>294</v>
       </c>
-      <c r="J6" s="33">
+      <c r="J6" s="31">
         <v>14</v>
       </c>
-      <c r="K6" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="18"/>
-      <c r="M6" s="33"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="Z6" s="18">
+      <c r="Y6" s="18">
         <v>1.15</v>
       </c>
-      <c r="AA6" s="23">
+      <c r="Z6" s="23">
         <v>0.670833333333333</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:27">
-      <c r="A7" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="35">
+    <row r="7" ht="14.25" spans="1:26">
+      <c r="A7" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="33">
         <v>3.52145333333333</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="33">
         <v>0.403249</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="34">
         <v>709</v>
       </c>
       <c r="E7" s="18">
@@ -2109,42 +1972,39 @@
       <c r="G7" s="18">
         <v>20.9</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="34">
         <v>637</v>
       </c>
       <c r="I7" s="18">
         <v>326</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="31">
         <v>14</v>
       </c>
-      <c r="K7" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="18"/>
-      <c r="M7" s="33"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="18"/>
       <c r="N7" s="18"/>
       <c r="O7" s="18"/>
       <c r="P7" s="18"/>
-      <c r="Q7" s="18"/>
-      <c r="Z7" s="18">
+      <c r="Y7" s="18">
         <v>1.15</v>
       </c>
-      <c r="AA7" s="23">
+      <c r="Z7" s="23">
         <v>0.661805555555556</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:27">
-      <c r="A8" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="35">
+    <row r="8" ht="14.25" spans="1:26">
+      <c r="A8" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="33">
         <v>2.15461333333333</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="33">
         <v>0.413413</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="34">
         <v>797</v>
       </c>
       <c r="E8" s="18">
@@ -2156,76 +2016,73 @@
       <c r="G8" s="18">
         <v>20.9</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="34">
         <v>782</v>
       </c>
       <c r="I8" s="18">
         <v>289</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="31">
         <v>13</v>
       </c>
-      <c r="K8" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="18">
+      <c r="K8" s="18">
         <v>7.03</v>
       </c>
-      <c r="M8" s="33" t="s">
-        <v>37</v>
+      <c r="L8" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="18">
+        <v>21.65</v>
       </c>
       <c r="N8" s="18">
-        <v>21.65</v>
+        <v>13.5</v>
       </c>
       <c r="O8" s="18">
-        <v>13.5</v>
-      </c>
-      <c r="P8" s="18">
         <v>7.44</v>
       </c>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="38">
+      <c r="P8" s="18"/>
+      <c r="Q8" s="35">
         <v>8.979</v>
       </c>
-      <c r="S8" s="39">
+      <c r="R8" s="36">
         <v>43.46</v>
       </c>
-      <c r="T8" s="39">
+      <c r="S8" s="36">
         <v>34.48</v>
       </c>
-      <c r="U8" s="38">
+      <c r="T8" s="35">
         <v>20.42</v>
       </c>
-      <c r="V8" s="38">
+      <c r="U8" s="35">
         <v>0.23</v>
       </c>
-      <c r="W8" s="38">
+      <c r="V8" s="35">
         <v>6</v>
       </c>
-      <c r="X8" s="38">
+      <c r="W8" s="35">
         <v>1.02</v>
       </c>
-      <c r="Y8" s="38">
+      <c r="X8" s="35">
         <v>12139.18</v>
       </c>
-      <c r="Z8" s="18">
+      <c r="Y8" s="18">
         <v>1.16</v>
       </c>
-      <c r="AA8" s="23">
+      <c r="Z8" s="23">
         <v>0.622222222222222</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:27">
-      <c r="A9" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="35">
+    <row r="9" ht="14.25" spans="1:26">
+      <c r="A9" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="33">
         <v>2.20711666666667</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="33">
         <v>1.239205</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="34">
         <v>753</v>
       </c>
       <c r="E9" s="18">
@@ -2237,44 +2094,41 @@
       <c r="G9" s="18">
         <v>20.9</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="34">
         <v>743</v>
       </c>
       <c r="I9" s="18">
         <v>274</v>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="31">
         <v>13</v>
       </c>
-      <c r="K9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L9" s="18"/>
-      <c r="M9" s="33"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="18"/>
       <c r="N9" s="18"/>
       <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18">
+      <c r="P9" s="18">
         <v>1.2</v>
       </c>
-      <c r="Z9" s="18">
+      <c r="Y9" s="18">
         <v>1.16</v>
       </c>
-      <c r="AA9" s="23">
+      <c r="Z9" s="23">
         <v>0.648611111111111</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:27">
-      <c r="A10" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="35">
+    <row r="10" ht="14.25" spans="1:26">
+      <c r="A10" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="33">
         <v>2.30323666666667</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="33">
         <v>0.418346666666667</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="34">
         <v>940</v>
       </c>
       <c r="E10" s="18">
@@ -2286,78 +2140,75 @@
       <c r="G10" s="18">
         <v>20.9</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="34">
         <v>600</v>
       </c>
       <c r="I10" s="18">
         <v>291</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10" s="31">
         <v>13</v>
       </c>
-      <c r="K10" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="18">
+      <c r="K10" s="18">
         <v>10.45</v>
       </c>
-      <c r="M10" s="33">
+      <c r="L10" s="31">
         <v>437</v>
       </c>
+      <c r="M10" s="18">
+        <v>695</v>
+      </c>
       <c r="N10" s="18">
-        <v>695</v>
+        <v>14.3</v>
       </c>
       <c r="O10" s="18">
-        <v>14.3</v>
+        <v>7.94</v>
       </c>
       <c r="P10" s="18">
-        <v>7.94</v>
-      </c>
-      <c r="Q10" s="18">
         <v>1.4</v>
       </c>
-      <c r="R10" s="38">
+      <c r="Q10" s="35">
         <v>17.11</v>
       </c>
-      <c r="S10" s="39">
+      <c r="R10" s="36">
         <v>81.49</v>
       </c>
-      <c r="T10" s="39">
+      <c r="S10" s="36">
         <v>64.37</v>
       </c>
-      <c r="U10" s="38">
+      <c r="T10" s="35">
         <v>33.3</v>
       </c>
-      <c r="V10" s="38">
+      <c r="U10" s="35">
         <v>7.11</v>
       </c>
-      <c r="W10" s="38">
+      <c r="V10" s="35">
         <v>21.59</v>
       </c>
-      <c r="X10" s="38">
+      <c r="W10" s="35">
         <v>2.98</v>
       </c>
-      <c r="Y10" s="38">
+      <c r="X10" s="35">
         <v>687.56</v>
       </c>
-      <c r="Z10" s="18">
+      <c r="Y10" s="18">
         <v>1.16</v>
       </c>
-      <c r="AA10" s="23">
+      <c r="Z10" s="23">
         <v>0.65625</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:27">
-      <c r="A11" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="35">
+    <row r="11" ht="14.25" spans="1:26">
+      <c r="A11" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="33">
         <v>2.11945666666667</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="33">
         <v>0.410596666666667</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="34">
         <v>1008</v>
       </c>
       <c r="E11" s="18">
@@ -2369,42 +2220,39 @@
       <c r="G11" s="18">
         <v>20.9</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="34">
         <v>584</v>
       </c>
       <c r="I11" s="18">
         <v>269</v>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="31">
         <v>1</v>
       </c>
-      <c r="K11" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" s="18"/>
-      <c r="M11" s="33"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="18"/>
       <c r="N11" s="18"/>
       <c r="O11" s="18"/>
       <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
-      <c r="Z11" s="18">
+      <c r="Y11" s="18">
         <v>1.19</v>
       </c>
-      <c r="AA11" s="23">
+      <c r="Z11" s="23">
         <v>0.4375</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="1:27">
-      <c r="A12" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="35">
+    <row r="12" ht="14.25" spans="1:26">
+      <c r="A12" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="33">
         <v>2.10388333333333</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="33">
         <v>0.413759666666667</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="34">
         <v>2841</v>
       </c>
       <c r="E12" s="18">
@@ -2416,42 +2264,39 @@
       <c r="G12" s="18">
         <v>20.9</v>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="34">
         <v>451</v>
       </c>
       <c r="I12" s="18">
         <v>275</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="31">
         <v>1</v>
       </c>
-      <c r="K12" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L12" s="18"/>
-      <c r="M12" s="33"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="18"/>
       <c r="P12" s="18"/>
-      <c r="Q12" s="18"/>
-      <c r="Z12" s="18">
+      <c r="Y12" s="18">
         <v>1.19</v>
       </c>
-      <c r="AA12" s="23">
+      <c r="Z12" s="23">
         <v>0.447916666666667</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="1:27">
-      <c r="A13" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="35">
+    <row r="13" ht="14.25" spans="1:26">
+      <c r="A13" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="33">
         <v>2.16274333333333</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="33">
         <v>0.417490333333333</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="34">
         <v>712</v>
       </c>
       <c r="E13" s="18">
@@ -2463,43 +2308,40 @@
       <c r="G13" s="18">
         <v>20.9</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="34">
         <v>515</v>
       </c>
       <c r="I13" s="18">
         <v>258</v>
       </c>
-      <c r="J13" s="33">
+      <c r="J13" s="31">
         <v>1</v>
       </c>
-      <c r="K13" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L13" s="18"/>
-      <c r="M13" s="33"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="18"/>
       <c r="N13" s="18"/>
       <c r="O13" s="18"/>
       <c r="P13" s="18"/>
-      <c r="Q13" s="18"/>
-      <c r="Z13" s="18">
+      <c r="Y13" s="18">
         <v>1.19</v>
       </c>
-      <c r="AA13" s="23">
+      <c r="Z13" s="23">
         <v>0.454861111111111</v>
       </c>
     </row>
-    <row r="14" ht="14.25" spans="1:27">
-      <c r="A14" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="42">
+    <row r="14" ht="14.25" spans="1:26">
+      <c r="A14" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="39">
         <v>2.13036333333333</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="33">
         <v>0.429711</v>
       </c>
-      <c r="D14" s="43" t="s">
-        <v>44</v>
+      <c r="D14" s="40" t="s">
+        <v>40</v>
       </c>
       <c r="E14" s="18">
         <v>650</v>
@@ -2510,76 +2352,73 @@
       <c r="G14" s="18">
         <v>20.9</v>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="34">
         <v>452</v>
       </c>
       <c r="I14" s="18">
         <v>268</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="31">
         <v>1</v>
       </c>
-      <c r="K14" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" s="18">
+      <c r="K14" s="18">
         <v>2.97</v>
       </c>
-      <c r="M14" s="33">
+      <c r="L14" s="31">
         <v>873</v>
       </c>
+      <c r="M14" s="18">
+        <v>1279</v>
+      </c>
       <c r="N14" s="18">
-        <v>1279</v>
+        <v>10.9</v>
       </c>
       <c r="O14" s="18">
-        <v>10.9</v>
-      </c>
-      <c r="P14" s="18">
         <v>7.63</v>
       </c>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="38">
+      <c r="P14" s="18"/>
+      <c r="Q14" s="35">
         <v>35.03</v>
       </c>
-      <c r="S14" s="39">
+      <c r="R14" s="36">
         <v>151.1</v>
       </c>
-      <c r="T14" s="39">
+      <c r="S14" s="36">
         <v>116</v>
       </c>
-      <c r="U14" s="38">
+      <c r="T14" s="35">
         <v>75.04</v>
       </c>
-      <c r="V14" s="38">
+      <c r="U14" s="35">
         <v>5.31</v>
       </c>
-      <c r="W14" s="38">
+      <c r="V14" s="35">
         <v>70.2</v>
       </c>
-      <c r="X14" s="38">
+      <c r="W14" s="35">
         <v>0.2</v>
       </c>
-      <c r="Y14" s="38">
+      <c r="X14" s="35">
         <v>590.45</v>
       </c>
-      <c r="Z14" s="18">
+      <c r="Y14" s="18">
         <v>1.19</v>
       </c>
-      <c r="AA14" s="23">
+      <c r="Z14" s="23">
         <v>0.465277777777778</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="1:27">
-      <c r="A15" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="42">
+    <row r="15" ht="14.25" spans="1:26">
+      <c r="A15" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="39">
         <v>2.21915333333333</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="33">
         <v>0.399433333333333</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="34">
         <v>1427</v>
       </c>
       <c r="E15" s="18">
@@ -2591,76 +2430,73 @@
       <c r="G15" s="18">
         <v>20.9</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="34">
         <v>677</v>
       </c>
       <c r="I15" s="18">
         <v>326</v>
       </c>
-      <c r="J15" s="33">
+      <c r="J15" s="31">
         <v>1</v>
       </c>
-      <c r="K15" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" s="33">
+      <c r="K15" s="31">
         <v>4.71</v>
       </c>
-      <c r="M15" s="33">
+      <c r="L15" s="31">
         <v>483</v>
       </c>
+      <c r="M15" s="18">
+        <v>810</v>
+      </c>
       <c r="N15" s="18">
-        <v>810</v>
+        <v>18.9</v>
       </c>
       <c r="O15" s="18">
-        <v>18.9</v>
-      </c>
-      <c r="P15" s="18">
         <v>9.25</v>
       </c>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="38">
+      <c r="P15" s="18"/>
+      <c r="Q15" s="35">
         <v>124</v>
       </c>
-      <c r="S15" s="39">
+      <c r="R15" s="36">
         <v>189</v>
       </c>
-      <c r="T15" s="39">
+      <c r="S15" s="36">
         <v>64.91</v>
       </c>
-      <c r="U15" s="38">
+      <c r="T15" s="35">
         <v>5.343</v>
       </c>
-      <c r="V15" s="38">
+      <c r="U15" s="35">
         <v>0.65</v>
       </c>
-      <c r="W15" s="38">
+      <c r="V15" s="35">
         <v>0.58</v>
       </c>
-      <c r="X15" s="38">
+      <c r="W15" s="35">
         <v>2.87</v>
       </c>
-      <c r="Y15" s="38">
+      <c r="X15" s="35">
         <v>1561.58</v>
       </c>
-      <c r="Z15" s="18">
+      <c r="Y15" s="18">
         <v>1.19</v>
       </c>
-      <c r="AA15" s="23">
+      <c r="Z15" s="23">
         <v>0.626388888888889</v>
       </c>
     </row>
-    <row r="16" ht="14.25" spans="1:27">
-      <c r="A16" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="42">
+    <row r="16" ht="14.25" spans="1:26">
+      <c r="A16" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="39">
         <v>2.13664</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="33">
         <v>0.406114333333333</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="34">
         <v>1225</v>
       </c>
       <c r="E16" s="18">
@@ -2672,42 +2508,39 @@
       <c r="G16" s="18">
         <v>20.9</v>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="34">
         <v>469</v>
       </c>
       <c r="I16" s="18">
         <v>294</v>
       </c>
-      <c r="J16" s="33">
+      <c r="J16" s="31">
         <v>1</v>
       </c>
-      <c r="K16" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="18"/>
       <c r="N16" s="18"/>
       <c r="O16" s="18"/>
       <c r="P16" s="18"/>
-      <c r="Q16" s="18"/>
-      <c r="Z16" s="18">
+      <c r="Y16" s="18">
         <v>1.19</v>
       </c>
-      <c r="AA16" s="23">
+      <c r="Z16" s="23">
         <v>0.642361111111111</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="1:27">
-      <c r="A17" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="42">
+    <row r="17" ht="14.25" spans="1:26">
+      <c r="A17" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="39">
         <v>2.21877666666667</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="33">
         <v>0.397960333333333</v>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="34">
         <v>1489</v>
       </c>
       <c r="E17" s="18">
@@ -2719,76 +2552,73 @@
       <c r="G17" s="18">
         <v>20.9</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="34">
         <v>491</v>
       </c>
       <c r="I17" s="18">
         <v>315</v>
       </c>
-      <c r="J17" s="33">
+      <c r="J17" s="31">
         <v>1</v>
       </c>
-      <c r="K17" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L17" s="33">
+      <c r="K17" s="31">
         <v>2.73</v>
       </c>
-      <c r="M17" s="33">
+      <c r="L17" s="31">
         <v>361</v>
       </c>
+      <c r="M17" s="18">
+        <v>484</v>
+      </c>
       <c r="N17" s="18">
-        <v>484</v>
+        <v>8.1</v>
       </c>
       <c r="O17" s="18">
-        <v>8.1</v>
-      </c>
-      <c r="P17" s="18">
         <v>8.76</v>
       </c>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="38">
+      <c r="P17" s="18"/>
+      <c r="Q17" s="35">
         <v>28.43</v>
       </c>
-      <c r="S17" s="39">
+      <c r="R17" s="36">
         <v>98.65</v>
       </c>
-      <c r="T17" s="39">
+      <c r="S17" s="36">
         <v>70.23</v>
       </c>
-      <c r="U17" s="38">
+      <c r="T17" s="35">
         <v>71.54</v>
       </c>
-      <c r="V17" s="38">
+      <c r="U17" s="35">
         <v>5.15</v>
       </c>
-      <c r="W17" s="38">
+      <c r="V17" s="35">
         <v>55.7</v>
       </c>
-      <c r="X17" s="38">
+      <c r="W17" s="35">
         <v>0.78</v>
       </c>
-      <c r="Y17" s="38">
+      <c r="X17" s="35">
         <v>940.06</v>
       </c>
-      <c r="Z17" s="18">
+      <c r="Y17" s="18">
         <v>1.19</v>
       </c>
-      <c r="AA17" s="23">
+      <c r="Z17" s="23">
         <v>0.649305555555556</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="1:27">
-      <c r="A18" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="42">
+    <row r="18" ht="14.25" spans="1:26">
+      <c r="A18" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="39">
         <v>2.72633666666667</v>
       </c>
       <c r="C18" s="1">
         <v>0.412017333333333</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="34">
         <v>3143</v>
       </c>
       <c r="E18" s="18">
@@ -2800,44 +2630,41 @@
       <c r="G18" s="18">
         <v>20.9</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="34">
         <v>483</v>
       </c>
       <c r="I18" s="18">
         <v>306</v>
       </c>
-      <c r="J18" s="33">
+      <c r="J18" s="31">
         <v>1</v>
       </c>
-      <c r="K18" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="18"/>
       <c r="N18" s="18"/>
       <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="18">
+      <c r="P18" s="18">
         <v>5</v>
       </c>
-      <c r="Z18" s="18">
+      <c r="Y18" s="18">
         <v>1.19</v>
       </c>
-      <c r="AA18" s="23">
+      <c r="Z18" s="23">
         <v>0.666666666666667</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="1:27">
-      <c r="A19" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="35">
+    <row r="19" ht="14.25" spans="1:26">
+      <c r="A19" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="33">
         <v>2.08234333333333</v>
       </c>
       <c r="C19" s="1">
         <v>0.395311666666667</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="34">
         <v>2379</v>
       </c>
       <c r="E19" s="18">
@@ -2849,34 +2676,31 @@
       <c r="G19" s="18">
         <v>20.9</v>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="37">
         <v>339</v>
       </c>
       <c r="I19" s="18">
         <v>159</v>
       </c>
-      <c r="J19" s="33">
+      <c r="J19" s="31">
         <v>1</v>
       </c>
-      <c r="K19" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="18"/>
       <c r="N19" s="18"/>
       <c r="O19" s="18"/>
       <c r="P19" s="18"/>
-      <c r="Q19" s="18"/>
-      <c r="Z19" s="18">
+      <c r="Y19" s="18">
         <v>1.19</v>
       </c>
-      <c r="AA19" s="23">
+      <c r="Z19" s="23">
         <v>0.685416666666667</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="1:27">
-      <c r="A20" s="41" t="s">
-        <v>50</v>
+    <row r="20" ht="14.25" spans="1:26">
+      <c r="A20" s="38" t="s">
+        <v>46</v>
       </c>
       <c r="B20" s="1">
         <v>2.12304</v>
@@ -2884,7 +2708,7 @@
       <c r="C20" s="1">
         <v>0.386967333333333</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="34">
         <v>1741</v>
       </c>
       <c r="E20" s="18">
@@ -2896,68 +2720,65 @@
       <c r="G20" s="18">
         <v>20.9</v>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="34">
         <v>630</v>
       </c>
       <c r="I20" s="18">
         <v>286</v>
       </c>
-      <c r="J20" s="33">
+      <c r="J20" s="31">
         <v>1</v>
       </c>
-      <c r="K20" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L20" s="33">
+      <c r="K20" s="31">
         <v>4.15</v>
       </c>
-      <c r="M20" s="33">
+      <c r="L20" s="31">
         <v>475</v>
       </c>
+      <c r="M20" s="18">
+        <v>731</v>
+      </c>
       <c r="N20" s="18">
-        <v>731</v>
+        <v>12.5</v>
       </c>
       <c r="O20" s="18">
-        <v>12.5</v>
-      </c>
-      <c r="P20" s="18">
         <v>9.02</v>
       </c>
-      <c r="Q20" s="18"/>
-      <c r="R20" s="38">
+      <c r="P20" s="18"/>
+      <c r="Q20" s="35">
         <v>44.99</v>
       </c>
-      <c r="S20" s="39">
+      <c r="R20" s="36">
         <v>144</v>
       </c>
-      <c r="T20" s="39">
+      <c r="S20" s="36">
         <v>99.03</v>
       </c>
-      <c r="U20" s="38">
+      <c r="T20" s="35">
         <v>18.97</v>
       </c>
-      <c r="V20" s="38">
+      <c r="U20" s="35">
         <v>1.35</v>
       </c>
-      <c r="W20" s="38">
+      <c r="V20" s="35">
         <v>5.22</v>
       </c>
-      <c r="X20" s="38">
+      <c r="W20" s="35">
         <v>0.08</v>
       </c>
-      <c r="Y20" s="38">
+      <c r="X20" s="35">
         <v>1204.21</v>
       </c>
-      <c r="Z20" s="18">
+      <c r="Y20" s="18">
         <v>1.19</v>
       </c>
-      <c r="AA20" s="23">
+      <c r="Z20" s="23">
         <v>0.694444444444444</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="1:27">
-      <c r="A21" s="41" t="s">
-        <v>51</v>
+    <row r="21" ht="14.25" spans="1:26">
+      <c r="A21" s="38" t="s">
+        <v>47</v>
       </c>
       <c r="B21" s="1">
         <v>2.60057</v>
@@ -2965,7 +2786,7 @@
       <c r="C21" s="1">
         <v>0.421040666666667</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="34">
         <v>1340</v>
       </c>
       <c r="E21" s="18">
@@ -2977,36 +2798,33 @@
       <c r="G21" s="18">
         <v>20.9</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="34">
         <v>373</v>
       </c>
       <c r="I21" s="18">
         <v>213</v>
       </c>
-      <c r="J21" s="33">
+      <c r="J21" s="31">
         <v>1</v>
       </c>
-      <c r="K21" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L21" s="18"/>
-      <c r="M21" s="33"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="18"/>
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
       <c r="P21" s="18"/>
-      <c r="Q21" s="18"/>
-      <c r="Z21" s="18">
+      <c r="Y21" s="18">
         <v>1.19</v>
       </c>
-      <c r="AA21" s="23">
+      <c r="Z21" s="23">
         <v>0.677777777777778</v>
       </c>
     </row>
-    <row r="22" ht="14.25" spans="1:27">
+    <row r="22" ht="14.25" spans="1:26">
       <c r="A22" s="18"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="33"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="31"/>
       <c r="F22" s="18"/>
       <c r="H22" s="18"/>
       <c r="J22" s="18"/>
@@ -3014,12 +2832,11 @@
       <c r="L22" s="18"/>
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
-    </row>
-    <row r="23" ht="14.25" spans="1:27">
+    </row>
+    <row r="23" ht="14.25" spans="1:26">
       <c r="A23" s="18"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="31"/>
       <c r="F23" s="18"/>
       <c r="H23" s="18"/>
       <c r="J23" s="18"/>
@@ -3027,12 +2844,11 @@
       <c r="L23" s="18"/>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-    </row>
-    <row r="24" ht="14.25" spans="1:27">
+    </row>
+    <row r="24" ht="14.25" spans="1:26">
       <c r="A24" s="18"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="31"/>
       <c r="F24" s="18"/>
       <c r="H24" s="18"/>
       <c r="J24" s="18"/>
@@ -3040,11 +2856,10 @@
       <c r="L24" s="18"/>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
-      <c r="O24" s="18"/>
-    </row>
-    <row r="25" ht="14.25" spans="1:27">
+    </row>
+    <row r="25" ht="14.25" spans="1:26">
       <c r="A25" s="18"/>
-      <c r="D25" s="33"/>
+      <c r="D25" s="31"/>
       <c r="F25" s="18"/>
       <c r="H25" s="18"/>
       <c r="J25" s="18"/>
@@ -3052,11 +2867,10 @@
       <c r="L25" s="18"/>
       <c r="M25" s="18"/>
       <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-    </row>
-    <row r="26" ht="14.25" spans="1:27">
+    </row>
+    <row r="26" ht="14.25" spans="1:26">
       <c r="A26" s="18"/>
-      <c r="D26" s="33"/>
+      <c r="D26" s="31"/>
       <c r="F26" s="18"/>
       <c r="H26" s="18"/>
       <c r="J26" s="18"/>
@@ -3064,11 +2878,10 @@
       <c r="L26" s="18"/>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-    </row>
-    <row r="27" ht="14.25" spans="1:27">
+    </row>
+    <row r="27" ht="14.25" spans="1:26">
       <c r="A27" s="18"/>
-      <c r="D27" s="33"/>
+      <c r="D27" s="31"/>
       <c r="F27" s="18"/>
       <c r="H27" s="18"/>
       <c r="J27" s="18"/>
@@ -3076,11 +2889,10 @@
       <c r="L27" s="18"/>
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
-    </row>
-    <row r="28" ht="14.25" spans="1:27">
+    </row>
+    <row r="28" ht="14.25" spans="1:26">
       <c r="A28" s="18"/>
-      <c r="D28" s="33"/>
+      <c r="D28" s="31"/>
       <c r="F28" s="18"/>
       <c r="H28" s="18"/>
       <c r="J28" s="18"/>
@@ -3088,11 +2900,10 @@
       <c r="L28" s="18"/>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
-      <c r="O28" s="18"/>
-    </row>
-    <row r="29" ht="14.25" spans="1:27">
+    </row>
+    <row r="29" ht="14.25" spans="1:26">
       <c r="A29" s="18"/>
-      <c r="D29" s="33"/>
+      <c r="D29" s="31"/>
       <c r="F29" s="18"/>
       <c r="H29" s="18"/>
       <c r="J29" s="18"/>
@@ -3100,11 +2911,10 @@
       <c r="L29" s="18"/>
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-    </row>
-    <row r="30" ht="14.25" spans="1:27">
+    </row>
+    <row r="30" ht="14.25" spans="1:26">
       <c r="A30" s="18"/>
-      <c r="D30" s="33"/>
+      <c r="D30" s="31"/>
       <c r="F30" s="18"/>
       <c r="H30" s="18"/>
       <c r="J30" s="18"/>
@@ -3112,11 +2922,10 @@
       <c r="L30" s="18"/>
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-    </row>
-    <row r="31" ht="14.25" spans="1:27">
+    </row>
+    <row r="31" ht="14.25" spans="1:26">
       <c r="A31" s="18"/>
-      <c r="D31" s="33"/>
+      <c r="D31" s="31"/>
       <c r="F31" s="18"/>
       <c r="H31" s="18"/>
       <c r="J31" s="18"/>
@@ -3124,11 +2933,10 @@
       <c r="L31" s="18"/>
       <c r="M31" s="18"/>
       <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
-    </row>
-    <row r="32" ht="14.25" spans="1:27">
+    </row>
+    <row r="32" ht="14.25" spans="1:26">
       <c r="A32" s="18"/>
-      <c r="D32" s="33"/>
+      <c r="D32" s="31"/>
       <c r="F32" s="18"/>
       <c r="H32" s="18"/>
       <c r="J32" s="18"/>
@@ -3136,11 +2944,10 @@
       <c r="L32" s="18"/>
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-    </row>
-    <row r="33" ht="14.25" spans="1:15">
+    </row>
+    <row r="33" ht="14.25" spans="1:14">
       <c r="A33" s="18"/>
-      <c r="D33" s="33"/>
+      <c r="D33" s="31"/>
       <c r="F33" s="18"/>
       <c r="H33" s="18"/>
       <c r="J33" s="18"/>
@@ -3148,11 +2955,10 @@
       <c r="L33" s="18"/>
       <c r="M33" s="18"/>
       <c r="N33" s="18"/>
-      <c r="O33" s="18"/>
-    </row>
-    <row r="34" ht="14.25" spans="1:15">
+    </row>
+    <row r="34" ht="14.25" spans="1:14">
       <c r="A34" s="18"/>
-      <c r="D34" s="33"/>
+      <c r="D34" s="31"/>
       <c r="F34" s="18"/>
       <c r="H34" s="18"/>
       <c r="J34" s="18"/>
@@ -3160,11 +2966,10 @@
       <c r="L34" s="18"/>
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
-    </row>
-    <row r="35" ht="14.25" spans="1:15">
+    </row>
+    <row r="35" ht="14.25" spans="1:14">
       <c r="A35" s="18"/>
-      <c r="D35" s="33"/>
+      <c r="D35" s="31"/>
       <c r="F35" s="18"/>
       <c r="H35" s="18"/>
       <c r="J35" s="18"/>
@@ -3172,11 +2977,10 @@
       <c r="L35" s="18"/>
       <c r="M35" s="18"/>
       <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-    </row>
-    <row r="36" ht="14.25" spans="1:15">
+    </row>
+    <row r="36" ht="14.25" spans="1:14">
       <c r="A36" s="18"/>
-      <c r="D36" s="33"/>
+      <c r="D36" s="31"/>
       <c r="F36" s="18"/>
       <c r="H36" s="18"/>
       <c r="J36" s="18"/>
@@ -3184,11 +2988,10 @@
       <c r="L36" s="18"/>
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
-      <c r="O36" s="18"/>
-    </row>
-    <row r="37" ht="14.25" spans="1:15">
+    </row>
+    <row r="37" ht="14.25" spans="1:14">
       <c r="A37" s="18"/>
-      <c r="D37" s="33"/>
+      <c r="D37" s="31"/>
       <c r="F37" s="18"/>
       <c r="H37" s="18"/>
       <c r="J37" s="18"/>
@@ -3196,11 +2999,10 @@
       <c r="L37" s="18"/>
       <c r="M37" s="18"/>
       <c r="N37" s="18"/>
-      <c r="O37" s="18"/>
-    </row>
-    <row r="38" ht="14.25" spans="1:15">
+    </row>
+    <row r="38" ht="14.25" spans="1:14">
       <c r="A38" s="18"/>
-      <c r="D38" s="33"/>
+      <c r="D38" s="31"/>
       <c r="F38" s="18"/>
       <c r="H38" s="18"/>
       <c r="J38" s="18"/>
@@ -3208,11 +3010,10 @@
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
-    </row>
-    <row r="39" ht="14.25" spans="1:15">
+    </row>
+    <row r="39" ht="14.25" spans="1:14">
       <c r="A39" s="18"/>
-      <c r="D39" s="33"/>
+      <c r="D39" s="31"/>
       <c r="F39" s="18"/>
       <c r="H39" s="18"/>
       <c r="J39" s="18"/>
@@ -3220,11 +3021,10 @@
       <c r="L39" s="18"/>
       <c r="M39" s="18"/>
       <c r="N39" s="18"/>
-      <c r="O39" s="18"/>
-    </row>
-    <row r="40" ht="14.25" spans="1:15">
+    </row>
+    <row r="40" ht="14.25" spans="1:14">
       <c r="A40" s="18"/>
-      <c r="D40" s="33"/>
+      <c r="D40" s="31"/>
       <c r="F40" s="18"/>
       <c r="H40" s="18"/>
       <c r="J40" s="18"/>
@@ -3232,7 +3032,6 @@
       <c r="L40" s="18"/>
       <c r="M40" s="18"/>
       <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3244,7 +3043,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG24"/>
+  <dimension ref="A1:AF24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -3253,30 +3052,30 @@
     <col min="5" max="5" width="13.875" customWidth="1"/>
     <col min="6" max="6" width="13.875" style="1" customWidth="1"/>
     <col min="7" max="8" width="10" customWidth="1"/>
-    <col min="13" max="13" width="11.625" customWidth="1"/>
-    <col min="14" max="14" width="11.875" customWidth="1"/>
-    <col min="15" max="15" width="14.375" customWidth="1"/>
-    <col min="17" max="17" width="16.375" style="1" customWidth="1"/>
-    <col min="18" max="20" width="12.375" style="1" customWidth="1"/>
-    <col min="21" max="22" width="14.75" customWidth="1"/>
-    <col min="23" max="23" width="14.5" customWidth="1"/>
-    <col min="24" max="24" width="14.75" customWidth="1"/>
-    <col min="25" max="25" width="15.125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="12.375" style="1" customWidth="1"/>
-    <col min="27" max="27" width="12.375" customWidth="1"/>
-    <col min="28" max="28" width="12.375" style="1" customWidth="1"/>
-    <col min="29" max="32" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="11.625" customWidth="1"/>
+    <col min="13" max="13" width="11.875" customWidth="1"/>
+    <col min="14" max="14" width="14.375" customWidth="1"/>
+    <col min="16" max="16" width="16.375" style="1" customWidth="1"/>
+    <col min="17" max="19" width="12.375" style="1" customWidth="1"/>
+    <col min="20" max="21" width="14.75" customWidth="1"/>
+    <col min="22" max="22" width="14.5" customWidth="1"/>
+    <col min="23" max="23" width="14.75" customWidth="1"/>
+    <col min="24" max="24" width="15.125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="12.375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="12.375" customWidth="1"/>
+    <col min="27" max="27" width="12.375" style="1" customWidth="1"/>
+    <col min="28" max="31" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:33">
+    <row r="1" ht="16.5" spans="1:32">
       <c r="A1" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>7</v>
@@ -3285,7 +3084,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -3297,27 +3096,27 @@
         <v>6</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="7" t="s">
         <v>17</v>
       </c>
       <c r="R1" s="7" t="s">
@@ -3326,52 +3125,49 @@
       <c r="S1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="U1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="W1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="X1" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z1" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA1" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB1" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC1" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD1" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z1" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA1" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB1" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC1" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD1" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE1" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="AG1" s="13" t="s">
+    </row>
+    <row r="2" ht="14.25" spans="1:32">
+      <c r="A2" s="14" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="2" ht="14.25" spans="1:33">
-      <c r="A2" s="14" t="s">
-        <v>27</v>
       </c>
       <c r="B2" s="15">
         <v>0.7388</v>
@@ -3400,31 +3196,28 @@
       <c r="J2" s="20">
         <v>17</v>
       </c>
-      <c r="K2" s="18" t="s">
-        <v>28</v>
-      </c>
+      <c r="K2" s="18"/>
       <c r="L2" s="18"/>
       <c r="M2" s="18"/>
       <c r="N2" s="18"/>
       <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
+      <c r="X2" s="21"/>
       <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="21"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="22"/>
       <c r="AC2" s="22"/>
       <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="18">
+      <c r="AE2" s="18">
         <v>4.1</v>
       </c>
-      <c r="AG2" s="23">
+      <c r="AF2" s="23">
         <v>0.459722222222222</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:33">
+    <row r="3" ht="14.25" spans="1:32">
       <c r="A3" s="14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" s="15">
         <v>45.7845666666667</v>
@@ -3453,65 +3246,62 @@
       <c r="J3" s="20">
         <v>17</v>
       </c>
-      <c r="K3" s="24" t="s">
-        <v>64</v>
+      <c r="K3" s="18">
+        <v>16.9</v>
       </c>
       <c r="L3" s="18">
-        <v>16.9</v>
+        <v>5.28</v>
       </c>
       <c r="M3" s="18">
-        <v>5.28</v>
+        <v>651</v>
       </c>
       <c r="N3" s="18">
-        <v>651</v>
+        <v>1102</v>
       </c>
       <c r="O3" s="18">
-        <v>1102</v>
-      </c>
-      <c r="P3" s="18">
         <v>8.32</v>
       </c>
+      <c r="P3" s="1">
+        <v>49.272</v>
+      </c>
       <c r="Q3" s="1">
-        <v>49.272</v>
+        <v>123.42</v>
       </c>
       <c r="R3" s="1">
-        <v>123.42</v>
-      </c>
-      <c r="S3" s="1">
         <v>74.16</v>
       </c>
+      <c r="S3">
+        <v>76.25</v>
+      </c>
       <c r="T3">
-        <v>76.25</v>
+        <v>5.08</v>
       </c>
       <c r="U3">
-        <v>5.08</v>
+        <v>70.76</v>
       </c>
       <c r="V3">
-        <v>70.76</v>
+        <v>0.08</v>
       </c>
       <c r="W3">
-        <v>0.08</v>
-      </c>
-      <c r="X3">
         <v>65.65</v>
       </c>
+      <c r="X3" s="21"/>
       <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="21"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="22"/>
       <c r="AC3" s="22"/>
       <c r="AD3" s="22"/>
-      <c r="AE3" s="22"/>
-      <c r="AF3" s="18">
+      <c r="AE3" s="18">
         <v>4.1</v>
       </c>
-      <c r="AG3" s="23">
+      <c r="AF3" s="23">
         <v>0.434027777777778</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:33">
+    <row r="4" ht="14.25" spans="1:32">
       <c r="A4" s="14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" s="15">
         <v>5.44646666666667</v>
@@ -3540,65 +3330,62 @@
       <c r="J4" s="20">
         <v>17</v>
       </c>
-      <c r="K4" s="24" t="s">
-        <v>64</v>
+      <c r="K4" s="18">
+        <v>17.5</v>
       </c>
       <c r="L4" s="18">
-        <v>17.5</v>
+        <v>3.96</v>
       </c>
       <c r="M4" s="18">
-        <v>3.96</v>
+        <v>394</v>
       </c>
       <c r="N4" s="18">
-        <v>394</v>
+        <v>648</v>
       </c>
       <c r="O4" s="18">
-        <v>648</v>
-      </c>
-      <c r="P4" s="18">
         <v>7.74</v>
       </c>
+      <c r="P4" s="1">
+        <v>29.35</v>
+      </c>
       <c r="Q4" s="1">
-        <v>29.35</v>
+        <v>70.1</v>
       </c>
       <c r="R4" s="1">
-        <v>70.1</v>
-      </c>
-      <c r="S4" s="1">
         <v>40.75</v>
       </c>
+      <c r="S4">
+        <v>22.21</v>
+      </c>
       <c r="T4">
-        <v>22.21</v>
+        <v>2.19</v>
       </c>
       <c r="U4">
-        <v>2.19</v>
+        <v>17.68</v>
       </c>
       <c r="V4">
-        <v>17.68</v>
+        <v>0.01</v>
       </c>
       <c r="W4">
-        <v>0.01</v>
-      </c>
-      <c r="X4">
         <v>31.78</v>
       </c>
+      <c r="X4" s="21"/>
       <c r="Y4" s="21"/>
-      <c r="Z4" s="21"/>
-      <c r="AA4" s="22"/>
-      <c r="AB4" s="21"/>
+      <c r="Z4" s="22"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="22"/>
       <c r="AC4" s="22"/>
       <c r="AD4" s="22"/>
-      <c r="AE4" s="22"/>
-      <c r="AF4" s="18">
+      <c r="AE4" s="18">
         <v>4.1</v>
       </c>
-      <c r="AG4" s="23">
+      <c r="AF4" s="23">
         <v>0.421527777777778</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:33">
+    <row r="5" ht="14.25" spans="1:32">
       <c r="A5" s="14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B5" s="15">
         <v>0.974833333333333</v>
@@ -3627,46 +3414,43 @@
       <c r="J5" s="20">
         <v>16</v>
       </c>
-      <c r="K5" s="18" t="s">
-        <v>65</v>
-      </c>
+      <c r="K5" s="18"/>
       <c r="L5" s="18"/>
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="T5"/>
+      <c r="S5"/>
+      <c r="X5" s="21">
+        <v>95.2694034576416</v>
+      </c>
       <c r="Y5" s="21">
-        <v>95.2694034576416</v>
-      </c>
-      <c r="Z5" s="21">
         <v>151.789012234385</v>
       </c>
-      <c r="AA5" s="22">
+      <c r="Z5" s="22">
         <v>1.54</v>
       </c>
-      <c r="AB5" s="21">
+      <c r="AA5" s="21">
         <v>35.7196414406254</v>
       </c>
+      <c r="AB5" s="22">
+        <v>8.41</v>
+      </c>
       <c r="AC5" s="22">
-        <v>8.41</v>
+        <v>3.9</v>
       </c>
       <c r="AD5" s="22">
-        <v>3.9</v>
-      </c>
-      <c r="AE5" s="22">
         <v>1.13</v>
       </c>
-      <c r="AF5" s="18">
+      <c r="AE5" s="18">
         <v>4.1</v>
       </c>
-      <c r="AG5" s="23">
+      <c r="AF5" s="23">
         <v>0.411111111111111</v>
       </c>
     </row>
-    <row r="6" ht="14.25" spans="1:33">
+    <row r="6" ht="14.25" spans="1:32">
       <c r="A6" s="14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B6" s="15">
         <v>0.631833333333333</v>
@@ -3695,32 +3479,29 @@
       <c r="J6" s="20">
         <v>16</v>
       </c>
-      <c r="K6" s="18" t="s">
-        <v>28</v>
-      </c>
+      <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="T6"/>
+      <c r="S6"/>
+      <c r="X6" s="21"/>
       <c r="Y6" s="21"/>
-      <c r="Z6" s="21"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="21"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="21"/>
+      <c r="AB6" s="22"/>
       <c r="AC6" s="22"/>
       <c r="AD6" s="22"/>
-      <c r="AE6" s="22"/>
-      <c r="AF6" s="18">
+      <c r="AE6" s="18">
         <v>4.1</v>
       </c>
-      <c r="AG6" s="23">
+      <c r="AF6" s="23">
         <v>0.402777777777778</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:33">
+    <row r="7" ht="14.25" spans="1:32">
       <c r="A7" s="14" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B7" s="15">
         <v>5.18586666666667</v>
@@ -3749,32 +3530,29 @@
       <c r="J7" s="20">
         <v>12</v>
       </c>
-      <c r="K7" s="18" t="s">
-        <v>28</v>
-      </c>
+      <c r="K7" s="18"/>
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
       <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="T7"/>
+      <c r="S7"/>
+      <c r="X7" s="21"/>
       <c r="Y7" s="21"/>
-      <c r="Z7" s="21"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="21"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="22"/>
       <c r="AC7" s="22"/>
       <c r="AD7" s="22"/>
-      <c r="AE7" s="22"/>
-      <c r="AF7" s="18">
+      <c r="AE7" s="18">
         <v>4.1</v>
       </c>
-      <c r="AG7" s="23">
+      <c r="AF7" s="23">
         <v>0.395833333333333</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:33">
+    <row r="8" ht="14.25" spans="1:32">
       <c r="A8" s="14" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B8" s="15">
         <v>4.5897</v>
@@ -3803,65 +3581,62 @@
       <c r="J8" s="20">
         <v>15</v>
       </c>
-      <c r="K8" s="24" t="s">
-        <v>64</v>
+      <c r="K8" s="18">
+        <v>15.4</v>
       </c>
       <c r="L8" s="18">
-        <v>15.4</v>
+        <v>3.72</v>
       </c>
       <c r="M8" s="18">
-        <v>3.72</v>
+        <v>534</v>
       </c>
       <c r="N8" s="18">
-        <v>534</v>
+        <v>888</v>
       </c>
       <c r="O8" s="18">
-        <v>888</v>
-      </c>
-      <c r="P8" s="18">
         <v>7.51</v>
       </c>
+      <c r="P8" s="1">
+        <v>29.826</v>
+      </c>
       <c r="Q8" s="1">
-        <v>29.826</v>
+        <v>109.5</v>
       </c>
       <c r="R8" s="1">
-        <v>109.5</v>
-      </c>
-      <c r="S8" s="1">
         <v>79.68</v>
       </c>
+      <c r="S8">
+        <v>45.28</v>
+      </c>
       <c r="T8">
-        <v>45.28</v>
+        <v>3.92</v>
       </c>
       <c r="U8">
-        <v>3.92</v>
+        <v>42.08</v>
       </c>
       <c r="V8">
-        <v>42.08</v>
+        <v>0.05</v>
       </c>
       <c r="W8">
-        <v>0.05</v>
-      </c>
-      <c r="X8">
         <v>26.18</v>
       </c>
+      <c r="X8" s="21"/>
       <c r="Y8" s="21"/>
-      <c r="Z8" s="21"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="21"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="21"/>
+      <c r="AB8" s="22"/>
       <c r="AC8" s="22"/>
       <c r="AD8" s="22"/>
-      <c r="AE8" s="22"/>
-      <c r="AF8" s="18">
+      <c r="AE8" s="18">
         <v>4.1</v>
       </c>
-      <c r="AG8" s="23">
+      <c r="AF8" s="23">
         <v>0.388888888888889</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:33">
+    <row r="9" ht="14.25" spans="1:32">
       <c r="A9" s="14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B9" s="15">
         <v>3.37646666666667</v>
@@ -3890,65 +3665,62 @@
       <c r="J9" s="20">
         <v>16</v>
       </c>
-      <c r="K9" s="24" t="s">
-        <v>64</v>
+      <c r="K9" s="18">
+        <v>15</v>
       </c>
       <c r="L9" s="18">
-        <v>15</v>
+        <v>2.89</v>
       </c>
       <c r="M9" s="18">
-        <v>2.89</v>
+        <v>345</v>
       </c>
       <c r="N9" s="18">
-        <v>345</v>
+        <v>572</v>
       </c>
       <c r="O9" s="18">
-        <v>572</v>
-      </c>
-      <c r="P9" s="18">
         <v>7.18</v>
       </c>
+      <c r="P9" s="1">
+        <v>20.25</v>
+      </c>
       <c r="Q9" s="1">
-        <v>20.25</v>
+        <v>82.39</v>
       </c>
       <c r="R9" s="1">
-        <v>82.39</v>
-      </c>
-      <c r="S9" s="1">
         <v>62.14</v>
       </c>
+      <c r="S9">
+        <v>6.96</v>
+      </c>
       <c r="T9">
-        <v>6.96</v>
+        <v>1.14</v>
       </c>
       <c r="U9">
-        <v>1.14</v>
+        <v>4.81</v>
       </c>
       <c r="V9">
-        <v>4.81</v>
+        <v>0.08</v>
       </c>
       <c r="W9">
-        <v>0.08</v>
-      </c>
-      <c r="X9">
         <v>16.39</v>
       </c>
+      <c r="X9" s="21"/>
       <c r="Y9" s="21"/>
-      <c r="Z9" s="21"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="21"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="21"/>
+      <c r="AB9" s="22"/>
       <c r="AC9" s="22"/>
       <c r="AD9" s="22"/>
-      <c r="AE9" s="22"/>
-      <c r="AF9" s="18">
+      <c r="AE9" s="18">
         <v>4.2</v>
       </c>
-      <c r="AG9" s="23">
+      <c r="AF9" s="23">
         <v>0.416666666666667</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:33">
+    <row r="10" ht="14.25" spans="1:32">
       <c r="A10" s="14" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B10" s="15">
         <v>77.2880333333333</v>
@@ -3977,65 +3749,62 @@
       <c r="J10" s="20">
         <v>16</v>
       </c>
-      <c r="K10" s="24" t="s">
-        <v>64</v>
+      <c r="K10" s="18">
+        <v>17.8</v>
       </c>
       <c r="L10" s="18">
-        <v>17.8</v>
+        <v>7.27</v>
       </c>
       <c r="M10" s="18">
-        <v>7.27</v>
+        <v>330</v>
       </c>
       <c r="N10" s="18">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="O10" s="18">
-        <v>580</v>
-      </c>
-      <c r="P10" s="18">
         <v>7.57</v>
       </c>
+      <c r="P10" s="1">
+        <v>15.04</v>
+      </c>
       <c r="Q10" s="1">
-        <v>15.04</v>
+        <v>74.97</v>
       </c>
       <c r="R10" s="1">
-        <v>74.97</v>
-      </c>
-      <c r="S10" s="1">
         <v>59.93</v>
       </c>
+      <c r="S10">
+        <v>13.62</v>
+      </c>
       <c r="T10">
-        <v>13.62</v>
+        <v>0.67</v>
       </c>
       <c r="U10">
-        <v>0.67</v>
+        <v>8.56</v>
       </c>
       <c r="V10">
-        <v>8.56</v>
+        <v>3.41</v>
       </c>
       <c r="W10">
-        <v>3.41</v>
-      </c>
-      <c r="X10">
         <v>14.06</v>
       </c>
+      <c r="X10" s="21"/>
       <c r="Y10" s="21"/>
-      <c r="Z10" s="21"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="21"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="21"/>
+      <c r="AB10" s="22"/>
       <c r="AC10" s="22"/>
       <c r="AD10" s="22"/>
-      <c r="AE10" s="22"/>
-      <c r="AF10" s="18">
+      <c r="AE10" s="18">
         <v>4.2</v>
       </c>
-      <c r="AG10" s="23">
+      <c r="AF10" s="23">
         <v>0.430555555555556</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:33">
+    <row r="11" ht="14.25" spans="1:32">
       <c r="A11" s="14" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" s="15">
         <v>588.9086</v>
@@ -4064,32 +3833,29 @@
       <c r="J11" s="20">
         <v>16</v>
       </c>
-      <c r="K11" s="18" t="s">
-        <v>28</v>
-      </c>
+      <c r="K11" s="18"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
       <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="T11"/>
+      <c r="S11"/>
+      <c r="X11" s="21"/>
       <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="21"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="21"/>
+      <c r="AB11" s="22"/>
       <c r="AC11" s="22"/>
       <c r="AD11" s="22"/>
-      <c r="AE11" s="22"/>
-      <c r="AF11" s="18">
+      <c r="AE11" s="18">
         <v>4.2</v>
       </c>
-      <c r="AG11" s="23">
+      <c r="AF11" s="23">
         <v>0.447916666666667</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="1:33">
+    <row r="12" ht="14.25" spans="1:32">
       <c r="A12" s="14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B12" s="15">
         <v>2.98416666666667</v>
@@ -4118,32 +3884,29 @@
       <c r="J12" s="20">
         <v>17</v>
       </c>
-      <c r="K12" s="18" t="s">
-        <v>28</v>
-      </c>
+      <c r="K12" s="18"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
-      <c r="T12"/>
+      <c r="S12"/>
+      <c r="X12" s="21"/>
       <c r="Y12" s="21"/>
-      <c r="Z12" s="21"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="21"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="22"/>
       <c r="AC12" s="22"/>
       <c r="AD12" s="22"/>
-      <c r="AE12" s="22"/>
-      <c r="AF12" s="18">
+      <c r="AE12" s="18">
         <v>4.2</v>
       </c>
-      <c r="AG12" s="23">
+      <c r="AF12" s="23">
         <v>0.458333333333333</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="1:33">
+    <row r="13" ht="14.25" spans="1:32">
       <c r="A13" s="14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B13" s="15">
         <v>1.39856666666667</v>
@@ -4172,32 +3935,29 @@
       <c r="J13" s="20">
         <v>16</v>
       </c>
-      <c r="K13" s="18" t="s">
-        <v>28</v>
-      </c>
+      <c r="K13" s="18"/>
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
       <c r="N13" s="18"/>
       <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="T13"/>
+      <c r="S13"/>
+      <c r="X13" s="21"/>
       <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="21"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="21"/>
+      <c r="AB13" s="22"/>
       <c r="AC13" s="22"/>
       <c r="AD13" s="22"/>
-      <c r="AE13" s="22"/>
-      <c r="AF13" s="18">
+      <c r="AE13" s="18">
         <v>4.8</v>
       </c>
-      <c r="AG13" s="23">
+      <c r="AF13" s="23">
         <v>0.395833333333333</v>
       </c>
     </row>
-    <row r="14" ht="14.25" spans="1:33">
+    <row r="14" ht="14.25" spans="1:32">
       <c r="A14" s="14" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B14" s="15">
         <v>464.353366666667</v>
@@ -4226,65 +3986,62 @@
       <c r="J14" s="20">
         <v>15</v>
       </c>
-      <c r="K14" s="24" t="s">
-        <v>64</v>
+      <c r="K14" s="18">
+        <v>17.7</v>
       </c>
       <c r="L14" s="18">
-        <v>17.7</v>
+        <v>0.95</v>
       </c>
       <c r="M14" s="18">
-        <v>0.95</v>
+        <v>503</v>
       </c>
       <c r="N14" s="18">
-        <v>503</v>
+        <v>872</v>
       </c>
       <c r="O14" s="18">
-        <v>872</v>
-      </c>
-      <c r="P14" s="18">
         <v>6.48</v>
       </c>
+      <c r="P14" s="1">
+        <v>40.452</v>
+      </c>
       <c r="Q14" s="1">
-        <v>40.452</v>
+        <v>98.52</v>
       </c>
       <c r="R14" s="1">
-        <v>98.52</v>
-      </c>
-      <c r="S14" s="1">
         <v>58.074</v>
       </c>
+      <c r="S14">
+        <v>16.93</v>
+      </c>
       <c r="T14">
-        <v>16.93</v>
+        <v>3.34</v>
       </c>
       <c r="U14">
-        <v>3.34</v>
+        <v>8.99</v>
       </c>
       <c r="V14">
-        <v>8.99</v>
+        <v>0.04</v>
       </c>
       <c r="W14">
-        <v>0.04</v>
-      </c>
-      <c r="X14">
         <v>36.28</v>
       </c>
+      <c r="X14" s="21"/>
       <c r="Y14" s="21"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="21"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="22"/>
       <c r="AC14" s="22"/>
       <c r="AD14" s="22"/>
-      <c r="AE14" s="22"/>
-      <c r="AF14" s="18">
+      <c r="AE14" s="18">
         <v>4.8</v>
       </c>
-      <c r="AG14" s="23">
+      <c r="AF14" s="23">
         <v>0.40625</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="1:33">
-      <c r="A15" s="25" t="s">
-        <v>66</v>
+    <row r="15" ht="14.25" spans="1:32">
+      <c r="A15" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="B15" s="15">
         <v>37.2458333333333</v>
@@ -4313,65 +4070,62 @@
       <c r="J15" s="20">
         <v>15</v>
       </c>
-      <c r="K15" s="24" t="s">
-        <v>64</v>
+      <c r="K15" s="18">
+        <v>19.3</v>
       </c>
       <c r="L15" s="18">
-        <v>19.3</v>
+        <v>4.88</v>
       </c>
       <c r="M15" s="18">
-        <v>4.88</v>
+        <v>428</v>
       </c>
       <c r="N15" s="18">
-        <v>428</v>
+        <v>773</v>
       </c>
       <c r="O15" s="18">
-        <v>773</v>
-      </c>
-      <c r="P15" s="18">
         <v>6.81</v>
       </c>
+      <c r="P15" s="1">
+        <v>39.21</v>
+      </c>
       <c r="Q15" s="1">
-        <v>39.21</v>
+        <v>77.07</v>
       </c>
       <c r="R15" s="1">
-        <v>77.07</v>
-      </c>
-      <c r="S15" s="1">
         <v>37.86</v>
       </c>
+      <c r="S15">
+        <v>5.01</v>
+      </c>
       <c r="T15">
-        <v>5.01</v>
+        <v>1.74</v>
       </c>
       <c r="U15">
-        <v>1.74</v>
+        <v>0.06</v>
       </c>
       <c r="V15">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="W15">
-        <v>0.02</v>
-      </c>
-      <c r="X15">
         <v>58.81</v>
       </c>
+      <c r="X15" s="21"/>
       <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="21"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="21"/>
+      <c r="AB15" s="22"/>
       <c r="AC15" s="22"/>
       <c r="AD15" s="22"/>
-      <c r="AE15" s="22"/>
-      <c r="AF15" s="18">
+      <c r="AE15" s="18">
         <v>4.8</v>
       </c>
-      <c r="AG15" s="23">
+      <c r="AF15" s="23">
         <v>0.416666666666667</v>
       </c>
     </row>
-    <row r="16" ht="14.25" spans="1:33">
+    <row r="16" ht="14.25" spans="1:32">
       <c r="A16" s="14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B16" s="15">
         <v>30.3663666666667</v>
@@ -4400,46 +4154,43 @@
       <c r="J16" s="20">
         <v>16</v>
       </c>
-      <c r="K16" s="18" t="s">
-        <v>65</v>
-      </c>
+      <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
       <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
-      <c r="T16"/>
+      <c r="S16"/>
+      <c r="X16" s="21">
+        <v>299.455604553223</v>
+      </c>
       <c r="Y16" s="21">
-        <v>299.455604553223</v>
-      </c>
-      <c r="Z16" s="21">
         <v>6513.92850797872</v>
       </c>
-      <c r="AA16" s="22">
+      <c r="Z16" s="22">
         <v>2.67</v>
       </c>
-      <c r="AB16" s="21">
+      <c r="AA16" s="21">
         <v>205.90521188175</v>
       </c>
+      <c r="AB16" s="22">
+        <v>9.15</v>
+      </c>
       <c r="AC16" s="22">
-        <v>9.15</v>
+        <v>953.79</v>
       </c>
       <c r="AD16" s="22">
-        <v>953.79</v>
-      </c>
-      <c r="AE16" s="22">
         <v>1.39</v>
       </c>
-      <c r="AF16" s="18">
+      <c r="AE16" s="18">
         <v>4.8</v>
       </c>
-      <c r="AG16" s="23">
+      <c r="AF16" s="23">
         <v>0.430555555555556</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="1:33">
+    <row r="17" ht="14.25" spans="1:32">
       <c r="A17" s="14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B17" s="15">
         <v>2.06716666666667</v>
@@ -4468,65 +4219,62 @@
       <c r="J17" s="20">
         <v>17</v>
       </c>
-      <c r="K17" s="24" t="s">
-        <v>64</v>
+      <c r="K17" s="18">
+        <v>16.2</v>
       </c>
       <c r="L17" s="18">
-        <v>16.2</v>
+        <v>3.35</v>
       </c>
       <c r="M17" s="18">
-        <v>3.35</v>
+        <v>608</v>
       </c>
       <c r="N17" s="18">
-        <v>608</v>
+        <v>1015</v>
       </c>
       <c r="O17" s="18">
-        <v>1015</v>
-      </c>
-      <c r="P17" s="18">
         <v>8.74</v>
       </c>
+      <c r="P17" s="1">
+        <v>106.2</v>
+      </c>
       <c r="Q17" s="1">
+        <v>203.28</v>
+      </c>
+      <c r="R17" s="1">
+        <v>97.02</v>
+      </c>
+      <c r="S17">
+        <v>124.82</v>
+      </c>
+      <c r="T17">
+        <v>8.29</v>
+      </c>
+      <c r="U17">
+        <v>103.68</v>
+      </c>
+      <c r="V17">
+        <v>0.52</v>
+      </c>
+      <c r="W17">
         <v>106.2</v>
       </c>
-      <c r="R17" s="1">
-        <v>203.28</v>
-      </c>
-      <c r="S17" s="1">
-        <v>97.02</v>
-      </c>
-      <c r="T17">
-        <v>124.82</v>
-      </c>
-      <c r="U17">
-        <v>8.29</v>
-      </c>
-      <c r="V17">
-        <v>103.68</v>
-      </c>
-      <c r="W17">
-        <v>0.52</v>
-      </c>
-      <c r="X17">
-        <v>106.2</v>
-      </c>
+      <c r="X17" s="21"/>
       <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="21"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="21"/>
+      <c r="AB17" s="22"/>
       <c r="AC17" s="22"/>
       <c r="AD17" s="22"/>
-      <c r="AE17" s="22"/>
-      <c r="AF17" s="18">
+      <c r="AE17" s="18">
         <v>4.8</v>
       </c>
-      <c r="AG17" s="23">
+      <c r="AF17" s="23">
         <v>0.604166666666667</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="1:33">
+    <row r="18" ht="14.25" spans="1:32">
       <c r="A18" s="14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B18" s="15">
         <v>2052.39033333333</v>
@@ -4555,32 +4303,29 @@
       <c r="J18" s="20">
         <v>17</v>
       </c>
-      <c r="K18" s="18" t="s">
-        <v>28</v>
-      </c>
+      <c r="K18" s="18"/>
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
       <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="T18"/>
+      <c r="S18"/>
+      <c r="X18" s="21"/>
       <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="21"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="21"/>
+      <c r="AB18" s="22"/>
       <c r="AC18" s="22"/>
       <c r="AD18" s="22"/>
-      <c r="AE18" s="22"/>
-      <c r="AF18" s="18">
+      <c r="AE18" s="18">
         <v>4.8</v>
       </c>
-      <c r="AG18" s="23">
+      <c r="AF18" s="23">
         <v>0.618055555555556</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="1:33">
+    <row r="19" ht="14.25" spans="1:32">
       <c r="A19" s="14" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B19" s="15">
         <v>211.763233333333</v>
@@ -4609,65 +4354,62 @@
       <c r="J19" s="20">
         <v>16</v>
       </c>
-      <c r="K19" s="24" t="s">
-        <v>64</v>
+      <c r="K19" s="18">
+        <v>20.3</v>
       </c>
       <c r="L19" s="18">
-        <v>20.3</v>
+        <v>2.87</v>
       </c>
       <c r="M19" s="18">
-        <v>2.87</v>
+        <v>379</v>
       </c>
       <c r="N19" s="18">
-        <v>379</v>
+        <v>753</v>
       </c>
       <c r="O19" s="18">
-        <v>753</v>
-      </c>
-      <c r="P19" s="18">
         <v>6.52</v>
       </c>
+      <c r="P19" s="1">
+        <v>72.18</v>
+      </c>
       <c r="Q19" s="1">
-        <v>72.18</v>
+        <v>97.8</v>
       </c>
       <c r="R19" s="1">
-        <v>97.8</v>
-      </c>
-      <c r="S19" s="1">
         <v>25.614</v>
       </c>
+      <c r="S19">
+        <v>30.97</v>
+      </c>
       <c r="T19">
-        <v>30.97</v>
+        <v>7.03</v>
       </c>
       <c r="U19">
-        <v>7.03</v>
+        <v>13.33</v>
       </c>
       <c r="V19">
-        <v>13.33</v>
+        <v>0.02</v>
       </c>
       <c r="W19">
-        <v>0.02</v>
-      </c>
-      <c r="X19">
         <v>522.47</v>
       </c>
+      <c r="X19" s="21"/>
       <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="22"/>
-      <c r="AB19" s="21"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="21"/>
+      <c r="AB19" s="22"/>
       <c r="AC19" s="22"/>
       <c r="AD19" s="22"/>
-      <c r="AE19" s="22"/>
-      <c r="AF19" s="18">
+      <c r="AE19" s="18">
         <v>4.8</v>
       </c>
-      <c r="AG19" s="23">
+      <c r="AF19" s="23">
         <v>0.439583333333333</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="1:33">
+    <row r="20" ht="14.25" spans="1:32">
       <c r="A20" s="14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B20" s="15">
         <v>2.2276</v>
@@ -4696,65 +4438,62 @@
       <c r="J20" s="20">
         <v>16</v>
       </c>
-      <c r="K20" s="24" t="s">
-        <v>64</v>
+      <c r="K20" s="18">
+        <v>16.3</v>
       </c>
       <c r="L20" s="18">
-        <v>16.3</v>
+        <v>6.83</v>
       </c>
       <c r="M20" s="18">
-        <v>6.83</v>
+        <v>588</v>
       </c>
       <c r="N20" s="18">
-        <v>588</v>
+        <v>988</v>
       </c>
       <c r="O20" s="18">
-        <v>988</v>
-      </c>
-      <c r="P20" s="18">
         <v>8.79</v>
       </c>
+      <c r="P20" s="1">
+        <v>65.52</v>
+      </c>
       <c r="Q20" s="1">
-        <v>65.52</v>
+        <v>132.96</v>
       </c>
       <c r="R20" s="1">
-        <v>132.96</v>
-      </c>
-      <c r="S20" s="1">
         <v>67.44</v>
       </c>
+      <c r="S20">
+        <v>98.31</v>
+      </c>
       <c r="T20">
-        <v>98.31</v>
+        <v>6.62</v>
       </c>
       <c r="U20">
-        <v>6.62</v>
+        <v>89.92</v>
       </c>
       <c r="V20">
-        <v>89.92</v>
+        <v>0.67</v>
       </c>
       <c r="W20">
-        <v>0.67</v>
-      </c>
-      <c r="X20">
         <v>57.26</v>
       </c>
+      <c r="X20" s="21"/>
       <c r="Y20" s="21"/>
-      <c r="Z20" s="21"/>
-      <c r="AA20" s="22"/>
-      <c r="AB20" s="21"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="21"/>
+      <c r="AB20" s="22"/>
       <c r="AC20" s="22"/>
       <c r="AD20" s="22"/>
-      <c r="AE20" s="22"/>
-      <c r="AF20" s="18">
+      <c r="AE20" s="18">
         <v>4.8</v>
       </c>
-      <c r="AG20" s="23">
+      <c r="AF20" s="23">
         <v>0.458333333333333</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="1:33">
+    <row r="21" ht="14.25" spans="1:32">
       <c r="A21" s="14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B21" s="15">
         <v>3.69026666666667</v>
@@ -4783,33 +4522,30 @@
       <c r="J21" s="20">
         <v>18</v>
       </c>
-      <c r="K21" s="18" t="s">
-        <v>28</v>
-      </c>
+      <c r="K21" s="18"/>
       <c r="L21" s="18"/>
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
-      <c r="P21" s="18"/>
+      <c r="X21" s="21"/>
       <c r="Y21" s="21"/>
-      <c r="Z21" s="21"/>
-      <c r="AA21" s="22"/>
-      <c r="AB21" s="21"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="21"/>
+      <c r="AB21" s="22"/>
       <c r="AC21" s="22"/>
       <c r="AD21" s="22"/>
-      <c r="AE21" s="22"/>
-      <c r="AF21" s="18">
+      <c r="AE21" s="18">
         <v>4.8</v>
       </c>
-      <c r="AG21" s="23">
+      <c r="AF21" s="23">
         <v>0.628472222222222</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
-      <c r="A23" s="26"/>
-    </row>
-    <row r="24" spans="1:33">
-      <c r="A24" s="26"/>
+    <row r="23" spans="1:32">
+      <c r="A23" s="24"/>
+    </row>
+    <row r="24" spans="1:32">
+      <c r="A24" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
